--- a/data/trans_dic/IP19C09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por otros motivos</t>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,42</t>
+          <t>0,0; 10,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,34</t>
+          <t>0,0; 13,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 6,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 8,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 18,03</t>
+          <t>3,47; 17,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 12,69</t>
+          <t>3,04; 13,17</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 12,13</t>
+          <t>1,42; 12,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,08</t>
+          <t>0,0; 11,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,16</t>
+          <t>0,0; 8,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,42</t>
+          <t>0,0; 9,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,94</t>
+          <t>0,86; 7,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,9</t>
+          <t>0,71; 6,15</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,29</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,53</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,06</t>
+          <t>0,91; 9,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,08</t>
+          <t>0,0; 12,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,33</t>
+          <t>0,0; 15,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,51</t>
+          <t>0,55; 5,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>0,0; 5,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,41</t>
+          <t>1,02; 10,66</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,25</t>
+          <t>0,84; 6,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,86</t>
+          <t>2,03; 8,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,98</t>
+          <t>1,31; 4,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,95</t>
+          <t>0,35; 3,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,33</t>
+          <t>0,72; 4,33</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,95</t>
+          <t>0,74; 7,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,3</t>
+          <t>0,86; 8,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,57</t>
+          <t>0,48; 4,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,45</t>
+          <t>0,44; 5,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,5</t>
+          <t>0,0; 10,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,07</t>
+          <t>0,0; 19,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,69</t>
+          <t>0,0; 13,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 13,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,22</t>
+          <t>0,87; 7,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,29</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,59</t>
+          <t>0,42; 2,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,29</t>
+          <t>0,82; 3,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,54</t>
+          <t>1,31; 4,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,32</t>
+          <t>2,02; 5,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,74</t>
+          <t>0,63; 2,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,15</t>
+          <t>1,37; 4,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,32</t>
+          <t>1,52; 3,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,66</t>
+          <t>0,89; 2,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,8</t>
+          <t>1,64; 3,83</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4251</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6174</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3482</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4551</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5734</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3078</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3540</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1729; 8766</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4320</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5152</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2775; 12030</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2532</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2668</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>575; 5021</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4037</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4108</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4629</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4976</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>663; 6023</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5245</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>764; 6622</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1791</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1791</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2189</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2969</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4384</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>487; 5053</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4870</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4917</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>484; 4928</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4610</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>617; 6440</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5189</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4354</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3531</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>890; 7201</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1949; 8594</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4481</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4878</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2548; 9699</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>647; 5552</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1480; 8931</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2853</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>608; 5968</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4037</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>602; 6011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3818</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>604; 5517</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>675; 8041</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4349</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2087</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4110</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5066</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4678</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4294</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>658; 5700</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4972</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3692</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3964</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>8278</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>15054</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>10511</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>16894</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1348; 7977</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2719; 10729</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4288; 14756</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6915; 17600</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2143; 9628</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4606; 14681</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10104; 22761</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5940; 17167</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>10921; 25482</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,35</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,03</t>
+          <t>0,0; 6,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,84</t>
+          <t>0,0; 15,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,24</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,66</t>
+          <t>0,0; 8,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 17,57</t>
+          <t>3,66; 17,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 6,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 13,17</t>
+          <t>2,76; 12,85</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,4</t>
+          <t>1,4; 12,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,09</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,84</t>
+          <t>0,0; 8,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,43</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,77</t>
+          <t>0,85; 7,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,15</t>
+          <t>0,61; 5,72</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>0,0; 15,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,47</t>
+          <t>0,92; 9,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,46</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,47</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,58</t>
+          <t>0,55; 5,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,66</t>
+          <t>1,02; 9,06</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,79</t>
+          <t>0,72; 7,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,94</t>
+          <t>2,03; 8,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,99</t>
+          <t>1,29; 4,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,02</t>
+          <t>0,35; 2,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,33</t>
+          <t>0,7; 4,38</t>
         </is>
       </c>
     </row>
@@ -1123,22 +1123,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,26</t>
+          <t>0,74; 7,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 5,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,58</t>
+          <t>0,88; 9,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,24</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,42</t>
+          <t>0,49; 4,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,18</t>
+          <t>0,41; 4,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,27</t>
+          <t>0,0; 9,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,72</t>
+          <t>0,0; 17,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,09</t>
+          <t>0,0; 12,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,99</t>
+          <t>0,0; 11,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,53</t>
+          <t>0,87; 7,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 6,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,47</t>
+          <t>0,58; 2,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,25</t>
+          <t>0,75; 3,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,5</t>
+          <t>1,3; 4,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,15</t>
+          <t>1,91; 5,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,85</t>
+          <t>0,59; 2,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,35</t>
+          <t>1,38; 4,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,42</t>
+          <t>1,48; 3,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,57</t>
+          <t>0,91; 2,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,83</t>
+          <t>1,66; 3,71</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3482</t>
+          <t>0; 4363</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4551</t>
+          <t>0; 3159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5734</t>
+          <t>0; 6377</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3078</t>
+          <t>0; 2941</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3540</t>
+          <t>0; 3450</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1729; 8766</t>
+          <t>1827; 8936</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4320</t>
+          <t>0; 4687</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5152</t>
+          <t>0; 5378</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2775; 12030</t>
+          <t>2518; 11739</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>575; 5021</t>
+          <t>568; 5059</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1812,37 +1812,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4037</t>
+          <t>0; 4047</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4108</t>
+          <t>0; 3432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4629</t>
+          <t>0; 4396</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4976</t>
+          <t>0; 4810</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>663; 6023</t>
+          <t>656; 6189</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5245</t>
+          <t>0; 4870</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>764; 6622</t>
+          <t>659; 6158</t>
         </is>
       </c>
     </row>
@@ -1970,42 +1970,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2969</t>
+          <t>0; 2956</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 4567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>487; 5053</t>
+          <t>490; 4855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4870</t>
+          <t>0; 2970</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4917</t>
+          <t>0; 3446</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>484; 4928</t>
+          <t>484; 5165</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4610</t>
+          <t>0; 5216</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>617; 6440</t>
+          <t>616; 5471</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3116</t>
+          <t>0; 3515</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3531</t>
+          <t>0; 4283</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>890; 7201</t>
+          <t>760; 7551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1949; 8594</t>
+          <t>1948; 8326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4481</t>
+          <t>0; 3976</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4878</t>
+          <t>0; 5566</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2548; 9699</t>
+          <t>2509; 9218</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>647; 5552</t>
+          <t>638; 5485</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1480; 8931</t>
+          <t>1451; 9035</t>
         </is>
       </c>
     </row>
@@ -2296,22 +2296,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>608; 5968</t>
+          <t>609; 5954</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4037</t>
+          <t>0; 3849</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>602; 6011</t>
+          <t>617; 6439</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3818</t>
+          <t>0; 3018</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>604; 5517</t>
+          <t>613; 5861</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>675; 8041</t>
+          <t>635; 7040</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4349</t>
+          <t>0; 3827</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4110</t>
+          <t>0; 3673</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5066</t>
+          <t>0; 4396</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4678</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2479,22 +2479,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>0; 3507</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>658; 5700</t>
+          <t>660; 5425</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4972</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3692</t>
+          <t>0; 3725</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1348; 7977</t>
+          <t>1869; 8992</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2719; 10729</t>
+          <t>2465; 10741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4288; 14756</t>
+          <t>4250; 14060</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6915; 17600</t>
+          <t>6523; 17382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2143; 9628</t>
+          <t>2010; 10080</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4606; 14681</t>
+          <t>4666; 14510</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10104; 22761</t>
+          <t>9846; 22244</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5940; 17167</t>
+          <t>6074; 17182</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10921; 25482</t>
+          <t>11024; 24715</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,39</t>
+          <t>3,6; 18,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 6,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,44</t>
+          <t>0,0; 9,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 17,91</t>
+          <t>0,0; 14,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 7,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,85</t>
+          <t>3,09; 12,69</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,36%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,49</t>
+          <t>0,0; 7,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 11,16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,42</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,15; 12,13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,36</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,27</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,39</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 7,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,98</t>
+          <t>0,83; 7,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 5,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,72</t>
+          <t>0,62; 5,9</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,92; 9,06</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,08</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 14,33</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,2</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 15,97</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,92; 9,1</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>0,0; 14,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,84</t>
+          <t>0,54; 5,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,06</t>
+          <t>1,01; 10,41</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,78%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>2,04; 8,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 7,12</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,66</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,71; 6,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,74</t>
+          <t>1,31; 4,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,98</t>
+          <t>0,35; 2,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,38</t>
+          <t>0,73; 4,33</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,87; 8,3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,87</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 7,24</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,82</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,73; 6,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,7</t>
+          <t>0,49; 4,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,54</t>
+          <t>0,6; 4,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>5,5%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>0,0; 11,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,22</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,5</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 17,07</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,94</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,43</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,16</t>
+          <t>0,87; 7,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,52%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,78</t>
+          <t>1,95; 5,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,26</t>
+          <t>0,59; 2,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,28</t>
+          <t>1,34; 4,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,09</t>
+          <t>0,57; 2,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,98</t>
+          <t>0,8; 3,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,3</t>
+          <t>1,32; 4,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,35</t>
+          <t>1,48; 3,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,57</t>
+          <t>0,94; 2,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,71</t>
+          <t>1,68; 3,8</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4251</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>764</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1923</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4363</t>
+          <t>0; 2490</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3159</t>
+          <t>0; 3704</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6377</t>
+          <t>1798; 8996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2941</t>
+          <t>0; 3748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3450</t>
+          <t>0; 4276</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1827; 8936</t>
+          <t>0; 5941</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4687</t>
+          <t>0; 4584</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5378</t>
+          <t>0; 6229</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2518; 11739</t>
+          <t>2825; 11589</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1883</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1297</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>568; 5059</t>
+          <t>0; 2624</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0; 5846</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4969</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>61; 4913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4047</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3432</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4396</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4810</t>
+          <t>0; 4004</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>656; 6189</t>
+          <t>642; 6159</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4870</t>
+          <t>0; 5313</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>659; 6158</t>
+          <t>667; 6358</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1791</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1341</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1791</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>493; 4835</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3547</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4557</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2956</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4567</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>490; 4855</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2970</t>
+          <t>0; 2994</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3446</t>
+          <t>0; 4157</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>484; 5165</t>
+          <t>482; 4868</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5216</t>
+          <t>0; 4893</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>616; 5471</t>
+          <t>609; 6284</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>616</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2946</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4573</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3515</t>
+          <t>1966; 8517</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4283</t>
+          <t>0; 4607</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>760; 7551</t>
+          <t>0; 4326</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1948; 8326</t>
+          <t>0; 3125</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3976</t>
+          <t>0; 4007</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5566</t>
+          <t>749; 6622</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2509; 9218</t>
+          <t>2545; 9685</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>638; 5485</t>
+          <t>645; 5427</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1451; 9035</t>
+          <t>1495; 8932</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2180</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>771</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>611; 5812</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2821</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>609; 5954</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3849</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>617; 6439</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3018</t>
+          <t>602; 5713</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3562</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>613; 5861</t>
+          <t>612; 5704</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>635; 7040</t>
+          <t>926; 6904</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3827</t>
+          <t>0; 3821</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3673</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4396</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>0; 3751</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5001</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4384</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4622</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3507</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>660; 5425</t>
+          <t>657; 5471</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>0; 4611</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3725</t>
+          <t>0; 2979</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>3964</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>8278</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>4862</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1869; 8992</t>
+          <t>6656; 18190</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2465; 10741</t>
+          <t>1997; 9282</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4250; 14060</t>
+          <t>4516; 14010</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6523; 17382</t>
+          <t>1844; 8378</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2010; 10080</t>
+          <t>2641; 10840</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4666; 14510</t>
+          <t>4344; 14899</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9846; 22244</t>
+          <t>9816; 22101</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6074; 17182</t>
+          <t>6259; 17737</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11024; 24715</t>
+          <t>11199; 25259</t>
         </is>
       </c>
     </row>
